--- a/output/pdf_financials_xlsx/EVOC.P.xlsx
+++ b/output/pdf_financials_xlsx/EVOC.P.xlsx
@@ -631,10 +631,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.07884099999999999</v>
+        <v>-0.07884099999999999</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.158898</v>
+        <v>-0.158898</v>
       </c>
     </row>
     <row r="17">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.07884099999999999</v>
+        <v>-0.07884099999999999</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.158898</v>
+        <v>-0.158898</v>
       </c>
     </row>
     <row r="21">
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.07884099999999999</v>
+        <v>-0.07884099999999999</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.158898</v>
+        <v>-0.158898</v>
       </c>
     </row>
     <row r="24">
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-7.9449</v>
+        <v>7.9449</v>
       </c>
     </row>
     <row r="27">
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.07884099999999999</v>
+        <v>-0.07884099999999999</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.158898</v>
+        <v>-0.158898</v>
       </c>
     </row>
     <row r="28">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.07884099999999999</v>
+        <v>-0.07884099999999999</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.158898</v>
+        <v>-0.158898</v>
       </c>
     </row>
     <row r="30">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1658,7 +1658,7 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.1374</v>
       </c>
     </row>
     <row r="93">
@@ -2556,7 +2556,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -3202,10 +3206,10 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0.07884099999999999</v>
+        <v>-0.07884099999999999</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.158898</v>
+        <v>-0.158898</v>
       </c>
     </row>
     <row r="36">

--- a/output/pdf_financials_xlsx/EVOC.P.xlsx
+++ b/output/pdf_financials_xlsx/EVOC.P.xlsx
@@ -877,10 +877,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.27523</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.619367</v>
       </c>
     </row>
     <row r="35">
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.27523</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.619367</v>
       </c>
     </row>
     <row r="37">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
